--- a/Phase 6_PS Cost Plan 07012026_docling_tables.xlsx
+++ b/Phase 6_PS Cost Plan 07012026_docling_tables.xlsx
@@ -592,8 +592,10 @@
           <t>Minor demolition and alteration works</t>
         </is>
       </c>
-      <c r="K3" s="4" t="n">
-        <v>0.93</v>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>93.0%</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -643,8 +645,10 @@
           <t>Eradication of plant growth</t>
         </is>
       </c>
-      <c r="K4" s="4" t="n">
-        <v>1</v>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -690,8 +694,10 @@
           <t>Steel frames</t>
         </is>
       </c>
-      <c r="K5" s="4" t="n">
-        <v>1</v>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -737,8 +743,10 @@
           <t>Floors</t>
         </is>
       </c>
-      <c r="K6" s="4" t="n">
-        <v>1</v>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -784,8 +792,10 @@
           <t>Roof structure</t>
         </is>
       </c>
-      <c r="K7" s="4" t="n">
-        <v>0.8110000000000001</v>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>81.1%</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -831,8 +841,10 @@
           <t>Stair/ramp structures</t>
         </is>
       </c>
-      <c r="K8" s="4" t="n">
-        <v>1</v>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -878,8 +890,10 @@
           <t>Walls and partitions</t>
         </is>
       </c>
-      <c r="K9" s="4" t="n">
-        <v>0.863</v>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>86.3%</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -925,8 +939,10 @@
           <t>External doors</t>
         </is>
       </c>
-      <c r="K10" s="4" t="n">
-        <v>1</v>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -972,8 +988,10 @@
           <t>Walls and partitions</t>
         </is>
       </c>
-      <c r="K11" s="4" t="n">
-        <v>1</v>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1019,8 +1037,10 @@
           <t>Internal doors</t>
         </is>
       </c>
-      <c r="K12" s="4" t="n">
-        <v>1</v>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1066,8 +1086,10 @@
           <t>Finishes to floors</t>
         </is>
       </c>
-      <c r="K13" s="4" t="n">
-        <v>1</v>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1113,8 +1135,10 @@
           <t>Wall finishes</t>
         </is>
       </c>
-      <c r="K14" s="4" t="n">
-        <v>1</v>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1160,8 +1184,10 @@
           <t>Finishes to ceilings</t>
         </is>
       </c>
-      <c r="K15" s="4" t="n">
-        <v>1</v>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1207,8 +1233,10 @@
           <t>General fittings, furnishings and equipment</t>
         </is>
       </c>
-      <c r="K16" s="4" t="n">
-        <v>0.607</v>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>60.7%</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1254,8 +1282,10 @@
           <t>Sanitary appliances</t>
         </is>
       </c>
-      <c r="K17" s="4" t="n">
-        <v>1</v>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1301,8 +1331,10 @@
           <t>Refuse disposal</t>
         </is>
       </c>
-      <c r="K18" s="4" t="n">
-        <v>0.727</v>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>72.7%</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1348,8 +1380,10 @@
           <t>Central heating</t>
         </is>
       </c>
-      <c r="K19" s="4" t="n">
-        <v>1</v>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1395,8 +1429,10 @@
           <t>Electrical mains and sub-mains distribution</t>
         </is>
       </c>
-      <c r="K20" s="4" t="n">
-        <v>1</v>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1442,8 +1478,10 @@
           <t>Lifts and enclosed hoists</t>
         </is>
       </c>
-      <c r="K21" s="4" t="n">
-        <v>1</v>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1489,8 +1527,10 @@
           <t>Builder’s work in connection with services</t>
         </is>
       </c>
-      <c r="K22" s="4" t="n">
-        <v>0.848</v>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>84.8%</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1536,8 +1576,10 @@
           <t>Eradication of plant growth</t>
         </is>
       </c>
-      <c r="K23" s="4" t="n">
-        <v>0.406</v>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>40.6%</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1583,8 +1625,10 @@
           <t>Foul drainage above ground</t>
         </is>
       </c>
-      <c r="K24" s="4" t="n">
-        <v>1</v>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1634,8 +1678,10 @@
           <t>Water mains supply</t>
         </is>
       </c>
-      <c r="K25" s="4" t="n">
-        <v>1</v>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1734,8 +1780,10 @@
           <t>Builder’s work in connection with services</t>
         </is>
       </c>
-      <c r="K27" s="4" t="n">
-        <v>0.373</v>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>37.3%</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1789,8 +1837,10 @@
           <t>Builder’s work in connection with services</t>
         </is>
       </c>
-      <c r="K28" s="4" t="n">
-        <v>0.415</v>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>41.5%</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1922,8 +1972,10 @@
           <t>Complete buildings</t>
         </is>
       </c>
-      <c r="K31" s="4" t="n">
-        <v>0.353</v>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>35.3%</t>
+        </is>
       </c>
     </row>
     <row r="34">
